--- a/docs/corpus/controle_echantillon.xlsx
+++ b/docs/corpus/controle_echantillon.xlsx
@@ -991,7 +991,7 @@
       <c r="O3" s="4" t="inlineStr"/>
       <c r="P3" s="4" t="inlineStr">
         <is>
-          <t>Début et fin coupés. chunk_text de 512 tokens exactement : il tient dans la limite de l'encodeur, mais serait tronqué de 3 tokens avec le préfixe E5 « passage: ».</t>
+          <t>Début et fin coupés. chunk_text de 512 tokens exactement : il tient dans la limite de l'encodeur, mais serait tronqué de 2 tokens avec le préfixe E5 « passage: ».</t>
         </is>
       </c>
     </row>
